--- a/artfynd/A 318-2024 artfynd.xlsx
+++ b/artfynd/A 318-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115162742</v>
+        <v>116012689</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 315-2024, Boh</t>
+          <t>Sollums Lång, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>327426</v>
+        <v>327308</v>
       </c>
       <c r="R2" t="n">
-        <v>6454983</v>
+        <v>6454827</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -792,12 +775,7 @@
         <v>116012704</v>
       </c>
       <c r="B3" t="n">
-        <v>94438</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116012650</v>
+        <v>116012705</v>
       </c>
       <c r="B4" t="n">
-        <v>94078</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116012652</v>
+        <v>116012658</v>
       </c>
       <c r="B5" t="n">
-        <v>94078</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>327376</v>
+        <v>327533</v>
       </c>
       <c r="R5" t="n">
-        <v>6454974</v>
+        <v>6455252</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116012672</v>
+        <v>116012686</v>
       </c>
       <c r="B6" t="n">
-        <v>96619</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>327531</v>
+        <v>327436</v>
       </c>
       <c r="R6" t="n">
-        <v>6455217</v>
+        <v>6455080</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116012658</v>
+        <v>116012687</v>
       </c>
       <c r="B7" t="n">
-        <v>95932</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1213,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1237,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>327533</v>
+        <v>327430</v>
       </c>
       <c r="R7" t="n">
-        <v>6455252</v>
+        <v>6455082</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116012689</v>
+        <v>116012688</v>
       </c>
       <c r="B8" t="n">
-        <v>74585</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1315,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>2606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1339,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>327308</v>
+        <v>327302</v>
       </c>
       <c r="R8" t="n">
-        <v>6454827</v>
+        <v>6454861</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,12 +1357,7 @@
         <v>116012703</v>
       </c>
       <c r="B9" t="n">
-        <v>94156</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,15 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116012705</v>
+        <v>116012649</v>
       </c>
       <c r="B10" t="n">
-        <v>94438</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1548,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>327436</v>
+        <v>327533</v>
       </c>
       <c r="R10" t="n">
-        <v>6455080</v>
+        <v>6455252</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,15 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116012686</v>
+        <v>116012650</v>
       </c>
       <c r="B11" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1626,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1712,15 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116012687</v>
+        <v>116012651</v>
       </c>
       <c r="B12" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1728,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>2810</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1752,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>327430</v>
+        <v>327389</v>
       </c>
       <c r="R12" t="n">
-        <v>6455082</v>
+        <v>6455010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1814,37 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116012667</v>
+        <v>116012652</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1854,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>327621</v>
+        <v>327376</v>
       </c>
       <c r="R13" t="n">
-        <v>6455174</v>
+        <v>6454974</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,11 +1818,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,15 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116012688</v>
+        <v>115162742</v>
       </c>
       <c r="B14" t="n">
-        <v>96292</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1937,37 +1855,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sollums Lång, Boh</t>
+          <t>A 315-2024, Boh</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>327302</v>
+        <v>327426</v>
       </c>
       <c r="R14" t="n">
-        <v>6454861</v>
+        <v>6454983</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1991,12 +1921,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-03-12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2011,31 +1941,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116012669</v>
+        <v>116012667</v>
       </c>
       <c r="B15" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2063,10 +1988,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>327437</v>
+        <v>327621</v>
       </c>
       <c r="R15" t="n">
-        <v>6455010</v>
+        <v>6455174</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,16 +2058,11 @@
         <v>116012668</v>
       </c>
       <c r="B16" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2237,15 +2157,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116012649</v>
+        <v>116012669</v>
       </c>
       <c r="B17" t="n">
-        <v>94078</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2253,21 +2168,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2810</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2277,10 +2192,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>327533</v>
+        <v>327437</v>
       </c>
       <c r="R17" t="n">
-        <v>6455252</v>
+        <v>6455010</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,6 +2230,11 @@
           <t>2024-04-15</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2336,6 +2256,103 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>116012672</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sollums Lång, Boh</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>327531</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6455217</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-04-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 318-2024 artfynd.xlsx
+++ b/artfynd/A 318-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012704</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012658</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012686</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012687</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012688</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012703</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012649</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012650</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012651</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012652</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012689</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1950,6 +2015,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115162742</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2052,6 +2122,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012667</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2154,6 +2229,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012668</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2256,6 +2336,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012669</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2353,8 +2438,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116012672</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>